--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9208F6-6194-4560-9235-B9727DA92193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE89A314-956A-4C95-B9D5-7BE62D854EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{B2810DB4-7512-4CE3-80EC-38F724CB9506}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="238">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -758,6 +758,9 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -7118,7 +7121,7 @@
     </row>
     <row r="153" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B153" s="36"/>
       <c r="C153" s="36" t="s">
@@ -7617,7 +7620,7 @@
     </row>
     <row r="166" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B166" s="36"/>
       <c r="C166" s="36" t="s">
